--- a/www/download/IND.abstract_labour.emp.s.mv.EXI382.xlsx
+++ b/www/download/IND.abstract_labour.emp.s.mv.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19097.64</t>
+          <t>19097640207.0913</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14507.826</t>
+          <t>14507826320.0021</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15448.211</t>
+          <t>15448211479.9975</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>15558.233</t>
+          <t>15558233079.996</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15815.484</t>
+          <t>15815484360.0018</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16001.517</t>
+          <t>16001517480.001</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16349.601</t>
+          <t>16349601493.3311</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16445.736</t>
+          <t>16445735800</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>16719.945</t>
+          <t>16719944800.0032</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>17008.748</t>
+          <t>17008748119.9935</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17336.604</t>
+          <t>17336604480.0033</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>17904.524</t>
+          <t>17904524039.9983</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>18312.139</t>
+          <t>18312138520.005</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>18844.801</t>
+          <t>18844801039.9999</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>19188.989</t>
+          <t>19188989039.9973</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>19242.531</t>
+          <t>19242531360.0076</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>19878.819</t>
+          <t>19878819479.998</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>20057.919</t>
+          <t>20057919439.999</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>20161.636</t>
+          <t>20161635519.999</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>18217.121</t>
+          <t>18217120938.7482</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>16871.245</t>
+          <t>16871244784.4711</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>17130.323</t>
+          <t>17130322807.0613</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>17634.785</t>
+          <t>17634785256.4646</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18370.706</t>
+          <t>18370706210.7791</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>17494.803</t>
+          <t>17494803266.5825</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17205.919</t>
+          <t>17205919147.3279</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>17256.738</t>
+          <t>17256737660.0571</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>7606.846</t>
+          <t>7606845527.58681</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5908.125</t>
+          <t>5908124999.99959</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5639.058</t>
+          <t>5639058000.0008</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>6498.084</t>
+          <t>6498084000.00022</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6575.463</t>
+          <t>6575463000.00189</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6672.371</t>
+          <t>6672371000.00139</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6380.48</t>
+          <t>6380479999.99792</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6433.899</t>
+          <t>6433898999.99918</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>6774.349</t>
+          <t>6774349000.00146</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6431.561</t>
+          <t>6431561000.00082</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>6840.452</t>
+          <t>6840451999.99942</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>6833.372</t>
+          <t>6833371999.99887</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>6882.429</t>
+          <t>6882429000.00111</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>6800.796</t>
+          <t>6800796000.00004</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>7019.697</t>
+          <t>7019696999.9988</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6813.569</t>
+          <t>6813568999.99573</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>6845.039</t>
+          <t>6845038999.99959</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6981.695</t>
+          <t>6981694999.99962</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>6930.619</t>
+          <t>6930618999.99826</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>6851.132</t>
+          <t>6851132147.63429</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>6876.885</t>
+          <t>6876885400.09145</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>7014.481</t>
+          <t>7014480697.08822</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>7210.408</t>
+          <t>7210408331.24225</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7457.122</t>
+          <t>7457121568.03781</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>7756.704</t>
+          <t>7756704192.413</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>7727.874</t>
+          <t>7727874279.24316</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>7728.427</t>
+          <t>7728427196.12385</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>7894.787</t>
+          <t>7894787320.46918</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5446.3</t>
+          <t>5446300000.00109</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>5504.5</t>
+          <t>5504500000.00004</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5696.2</t>
+          <t>5696199999.99943</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5652.2</t>
+          <t>5652199999.99782</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6379.5</t>
+          <t>6379500000.00024</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6558.2</t>
+          <t>6558200000.00022</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6621.4</t>
+          <t>6621400000.00076</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6585.4</t>
+          <t>6585399999.9998</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>6562.8</t>
+          <t>6562799999.99999</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>6604.7</t>
+          <t>6604699999.99968</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6667.2</t>
+          <t>6667199999.99852</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>6782.2</t>
+          <t>6782199999.99948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>6913.8</t>
+          <t>6913800000.0014</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7010000000.00171</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>6914.6</t>
+          <t>6914600000.00112</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>6987.1</t>
+          <t>6987099999.99979</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>7099.3</t>
+          <t>7099300000.00237</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>7163.9</t>
+          <t>7163900000.00089</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>7150.906</t>
+          <t>7150906220.16126</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>7059.729</t>
+          <t>7059728960.53178</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>7248.264</t>
+          <t>7248263614.15663</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>7357.461</t>
+          <t>7357460821.22353</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7493.553</t>
+          <t>7493552911.71357</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>7632.884</t>
+          <t>7632883629.44109</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>7779.707</t>
+          <t>7779707357.70618</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>7764.48</t>
+          <t>7764479941.7072</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10227.209</t>
+          <t>10227209464.5633</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>6573.78</t>
+          <t>6573779680.00082</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6410.759</t>
+          <t>6410758639.99939</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6100.288</t>
+          <t>6100288480.00096</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>5815.83</t>
+          <t>5815829760.00081</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5950.544</t>
+          <t>5950544079.99921</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5485.504</t>
+          <t>5485504440.0003</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5824.643</t>
+          <t>5824642719.99998</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5819.111</t>
+          <t>5819111479.99978</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6017.383</t>
+          <t>6017383319.9998</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6274.409</t>
+          <t>6274409440.00117</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>6377.546</t>
+          <t>6377545719.99984</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>6687.298</t>
+          <t>6687298279.99894</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>6946.884</t>
+          <t>6946883839.99818</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>7178.934</t>
+          <t>7178933840.00061</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>6758.883</t>
+          <t>6758882520.00165</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>6426.469</t>
+          <t>6426468879.99931</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6201.404</t>
+          <t>6201403519.99875</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6119.407</t>
+          <t>6119406799.99922</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>5812.36</t>
+          <t>5812360247.23949</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>6194.427</t>
+          <t>6194426501.58921</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>6550.217</t>
+          <t>6550216728.36806</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>6758.492</t>
+          <t>6758491846.82007</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7317.713</t>
+          <t>7317713470.79959</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>7982.493</t>
+          <t>7982492683.94338</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>8616.463</t>
+          <t>8616463156.35127</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>9054.641</t>
+          <t>9054640595.91263</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>186656.526</t>
+          <t>186656525506.772</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>163323.3</t>
+          <t>163323299999.937</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>159003.6</t>
+          <t>159003599999.965</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>162086.1</t>
+          <t>162086099999.972</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>163275.8</t>
+          <t>163275799999.992</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>167222.8</t>
+          <t>167222800000.007</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>168996.4</t>
+          <t>168996400000.032</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>174794.2</t>
+          <t>174794199999.964</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>177294.8</t>
+          <t>177294799999.999</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>179369</t>
+          <t>179368999999.939</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>188175.5</t>
+          <t>188175500000.021</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>192590.1</t>
+          <t>192590100000.036</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>196087.4</t>
+          <t>196087399999.975</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>198229</t>
+          <t>198228999999.983</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>200180.4</t>
+          <t>200180400000.042</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>202133.3</t>
+          <t>202133299999.998</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>203264.9</t>
+          <t>203264899999.891</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>204397</t>
+          <t>204397000000.022</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>207135.9</t>
+          <t>207135899999.98</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>200665.358</t>
+          <t>200665358062.658</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>197078.91</t>
+          <t>197078909720.836</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>165989.879</t>
+          <t>165989879342.868</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>167999.035</t>
+          <t>167999035398.614</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>186701.928</t>
+          <t>186701927513.837</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>167538.164</t>
+          <t>167538163734.947</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>172283.954</t>
+          <t>172283954069.918</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>168133.361</t>
+          <t>168133360743.209</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>24884.716</t>
+          <t>24884715891.5985</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23719.492</t>
+          <t>23719491999.996</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21711.029</t>
+          <t>21711028999.9954</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22951.165</t>
+          <t>22951165000.0009</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>23392.199</t>
+          <t>23392199000.0057</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>26231.013</t>
+          <t>26231013000.0021</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26804.392</t>
+          <t>26804391999.9978</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26856.964</t>
+          <t>26856964000.0007</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27348.689</t>
+          <t>27348688999.9959</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>27718.698</t>
+          <t>27718697999.9945</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>28497.801</t>
+          <t>28497801000.0082</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>26299.86</t>
+          <t>26299859999.9983</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>29149.991</t>
+          <t>29149990999.9969</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>29741.591</t>
+          <t>29741590999.9995</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>30108.649</t>
+          <t>30108648999.9963</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>27203.083</t>
+          <t>27203082999.9994</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>29580.123</t>
+          <t>29580122999.9906</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>30027.806</t>
+          <t>30027806000.0042</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>30541.025</t>
+          <t>30541025000.005</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>28431.563</t>
+          <t>28431563102.2932</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>26426.583</t>
+          <t>26426583135.0825</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26317.661</t>
+          <t>26317660721.2692</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>25215.392</t>
+          <t>25215391848.2891</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>25195.53</t>
+          <t>25195529723.3985</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>24350.853</t>
+          <t>24350853309.1604</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>25614.49</t>
+          <t>25614489719.3908</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>25074.842</t>
+          <t>25074842275.9537</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3226007.93</t>
+          <t>3226007929583.45</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1322267.187</t>
+          <t>1322267187280.25</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1340365.835</t>
+          <t>1340365835120.12</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1352111.089</t>
+          <t>1352111088639.52</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1313778.722</t>
+          <t>1313778721839.82</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1320105.998</t>
+          <t>1320105997600.25</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1316373.231</t>
+          <t>1316373230639.41</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1313002.56</t>
+          <t>1313002560480.1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1319761.626</t>
+          <t>1319761625520.36</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1301219.734</t>
+          <t>1301219733840.37</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1289135.599</t>
+          <t>1289135598919.79</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1366161.383</t>
+          <t>1366161383080.44</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1387438.056</t>
+          <t>1387438055640.18</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1334233.856</t>
+          <t>1334233855760.22</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1273554.479</t>
+          <t>1273554479079.61</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1239195.747</t>
+          <t>1239195747400.09</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1316292.774</t>
+          <t>1316292773639.89</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1393284.294</t>
+          <t>1393284293959.95</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1423831.754</t>
+          <t>1423831754280.04</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1504344.065</t>
+          <t>1504344064721.83</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1618832.304</t>
+          <t>1618832303847.31</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>1969463.893</t>
+          <t>1969463892996.68</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1954212.4</t>
+          <t>1954212400428.52</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2118014.253</t>
+          <t>2118014252840.92</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2220813.821</t>
+          <t>2220813820829.07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2447788.289</t>
+          <t>2447788289194.64</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2577679.32</t>
+          <t>2577679319614.35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1024.903</t>
+          <t>1024902967.85932</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>550.339</t>
+          <t>550339000.000105</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>558.81</t>
+          <t>558810000.000059</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>567.856</t>
+          <t>567855999.999809</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>576.647</t>
+          <t>576647000.000091</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>580.265</t>
+          <t>580264999.999769</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>604.433</t>
+          <t>604432999.999886</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>620.968</t>
+          <t>620968000.000055</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>638.417</t>
+          <t>638417000.000103</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>655.987</t>
+          <t>655987000.000023</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>686.864</t>
+          <t>686864000.000062</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>718.428</t>
+          <t>718428000</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>735.148</t>
+          <t>735147999.999951</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>774.107</t>
+          <t>774107000.000145</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>796.951</t>
+          <t>796951000.000003</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>786.771</t>
+          <t>786771000.000135</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>814.256</t>
+          <t>814256000.000087</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>805.886</t>
+          <t>805886000.000032</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>790.685</t>
+          <t>790684999.99994</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>728.828</t>
+          <t>728828094.964939</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>734.061</t>
+          <t>734060734.740077</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>770.833</t>
+          <t>770833001.495182</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>868.364</t>
+          <t>868364471.523196</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>891.839</t>
+          <t>891838971.554538</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>955.443</t>
+          <t>955442684.811026</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>999.765</t>
+          <t>999765279.808281</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>1028.557</t>
+          <t>1028556994.33781</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12305.186</t>
+          <t>12305186074.28</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9325.123</t>
+          <t>9325123000.00054</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9082.699</t>
+          <t>9082699000.00087</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9466.723</t>
+          <t>9466722999.99986</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9400.914</t>
+          <t>9400913999.99816</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9277.541</t>
+          <t>9277540999.9997</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9211.65</t>
+          <t>9211650000.00095</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8655.611</t>
+          <t>8655610999.9979</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>8852.681</t>
+          <t>8852681000.00122</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>8560.248</t>
+          <t>8560248000.0002</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>8773.855</t>
+          <t>8773855000.00094</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>8944.482</t>
+          <t>8944482000.00019</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>8975.089</t>
+          <t>8975089000.00128</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>9087.596</t>
+          <t>9087596000.00118</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>9313.63</t>
+          <t>9313630000.00136</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>9089.582</t>
+          <t>9089582000.00025</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>9101.091</t>
+          <t>9101091000.00175</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>8886.894</t>
+          <t>8886894000.00016</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>8994.842</t>
+          <t>8994842000.00007</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>8484.527</t>
+          <t>8484526622.42906</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>8208.031</t>
+          <t>8208031214.23864</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8739.988</t>
+          <t>8739988324.18744</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>8915.057</t>
+          <t>8915056618.94588</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9532.349</t>
+          <t>9532348629.10104</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>10343.116</t>
+          <t>10343115740.3291</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10997.256</t>
+          <t>10997256452.8583</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>11175.184</t>
+          <t>11175184263.0297</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>66615.956</t>
+          <t>66615956342.1206</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>58083.9</t>
+          <t>58083899999.9965</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>57352.2</t>
+          <t>57352200000.0111</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>56907.1</t>
+          <t>56907099999.9991</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>57362.9</t>
+          <t>57362899999.9863</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>57716.9</t>
+          <t>57716900000.0125</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>57960</t>
+          <t>57959999999.9807</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>57401.1</t>
+          <t>57401100000.0125</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>56704.2</t>
+          <t>56704200000.0026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>55851000000.0131</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>55386.9</t>
+          <t>55386900000.0068</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>55500.1</t>
+          <t>55500099999.9919</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>56465</t>
+          <t>56465000000.0007</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>57439.1</t>
+          <t>57439099999.993</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57950</t>
+          <t>57949999999.9866</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>56133.9</t>
+          <t>56133900000.0017</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>57013.1</t>
+          <t>57013099999.9871</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>57914.1</t>
+          <t>57914099999.9958</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>57763</t>
+          <t>57762999999.9933</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>58439.835</t>
+          <t>58439835150.6908</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>60568.02</t>
+          <t>60568019866.4359</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>60132.111</t>
+          <t>60132110634.2479</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>60811.469</t>
+          <t>60811468542.7504</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>64373.414</t>
+          <t>64373414211.2917</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>63003.347</t>
+          <t>63003347070.457</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>63897.953</t>
+          <t>63897952780.7039</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>65968.562</t>
+          <t>65968561950.3728</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4999.609</t>
+          <t>4999609451.39184</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4921.162</t>
+          <t>4921161999.99928</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4931.688</t>
+          <t>4931687999.99992</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>4748.265</t>
+          <t>4748265000.00036</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4247.673</t>
+          <t>4247673000.00013</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5283.839</t>
+          <t>5283838999.99931</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5099.731</t>
+          <t>5099730999.99973</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5178.395</t>
+          <t>5178394999.99954</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>5281.112</t>
+          <t>5281112000.00102</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5096.332</t>
+          <t>5096332000.00074</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>5122.786</t>
+          <t>5122785999.99976</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>5015.492</t>
+          <t>5015491999.99899</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>5403.361</t>
+          <t>5403361000.00005</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>5410.806</t>
+          <t>5410806000.00122</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>5241.104</t>
+          <t>5241103999.99949</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>4974.992</t>
+          <t>4974992000.00079</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>4958.534</t>
+          <t>4958534000.00192</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4969.841</t>
+          <t>4969841000.00048</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>4920.642</t>
+          <t>4920641999.9995</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>5035.135</t>
+          <t>5035134751.20105</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>5315.74</t>
+          <t>5315739973.40009</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5139.539</t>
+          <t>5139538902.14448</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>5155.566</t>
+          <t>5155566113.50021</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5183.932</t>
+          <t>5183932354.49102</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>4811.529</t>
+          <t>4811528777.06346</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>4755.058</t>
+          <t>4755058091.5443</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>4757.086</t>
+          <t>4757086444.44758</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>36500.716</t>
+          <t>36500716125.1982</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25676.724</t>
+          <t>25676724000.0017</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26071.86</t>
+          <t>26071859999.9982</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>27260.777</t>
+          <t>27260777000.0063</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>28482.155</t>
+          <t>28482155000.0059</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>31060.884</t>
+          <t>31060883999.9999</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31882.031</t>
+          <t>31882031000.0083</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>33082.922</t>
+          <t>33082921999.9957</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>34624.508</t>
+          <t>34624508000.0016</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>35276.335</t>
+          <t>35276335000.0029</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>37108.969</t>
+          <t>37108968999.9996</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>39989.019</t>
+          <t>39989019000.0058</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>41381.202</t>
+          <t>41381202000.0017</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>42579.125</t>
+          <t>42579124999.9951</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>41105.018</t>
+          <t>41105018000.0037</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>37872.225</t>
+          <t>37872225000.0054</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>36982.035</t>
+          <t>36982034999.9897</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>36223.614</t>
+          <t>36223613999.9945</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>34334.308</t>
+          <t>34334308000.0037</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>33069.119</t>
+          <t>33069118938.7597</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>32721.579</t>
+          <t>32721578935.3163</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>34186.183</t>
+          <t>34186182805.8568</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>34648.866</t>
+          <t>34648866367.8214</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>35017.46</t>
+          <t>35017459879.3931</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>35808.752</t>
+          <t>35808751644.3015</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>35578.385</t>
+          <t>35578385268.5515</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>36374.493</t>
+          <t>36374492609.8103</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2624.057</t>
+          <t>2624056679.20521</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1287.36</t>
+          <t>1287360000.00011</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1226.864</t>
+          <t>1226864000.00016</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1222.093</t>
+          <t>1222092999.99974</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1241.477</t>
+          <t>1241476999.99979</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1156.999</t>
+          <t>1156998999.99997</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1196.229</t>
+          <t>1196228999.99974</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1182.544</t>
+          <t>1182544000.00002</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1197.808</t>
+          <t>1197808000.0003</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1188.383</t>
+          <t>1188382999.99983</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1222.234</t>
+          <t>1222234000.00017</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1265.252</t>
+          <t>1265251999.9998</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1339.137</t>
+          <t>1339137000.00013</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1349.415</t>
+          <t>1349415000.00004</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1345.608</t>
+          <t>1345608000</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1172.661</t>
+          <t>1172660999.99969</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1146.707</t>
+          <t>1146707000.00001</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1223.029</t>
+          <t>1223029000.0001</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1236.751</t>
+          <t>1236751000.00027</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1277.521</t>
+          <t>1277521014.85041</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1216.715</t>
+          <t>1216714733.50015</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>1253.191</t>
+          <t>1253191474.66119</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1326.554</t>
+          <t>1326553638.66803</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1356.757</t>
+          <t>1356757367.59699</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1494.572</t>
+          <t>1494571895.72668</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>1616.92</t>
+          <t>1616920043.81368</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1644.894</t>
+          <t>1644893727.35019</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4546.835</t>
+          <t>4546835431.66232</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4044.12</t>
+          <t>4044120000.00004</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4173.152</t>
+          <t>4173151999.99902</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4565.122</t>
+          <t>4565121999.99841</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4501.088</t>
+          <t>4501087999.99945</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4758.344</t>
+          <t>4758343999.9995</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4747.796</t>
+          <t>4747795999.99841</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4762.79</t>
+          <t>4762789999.99951</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4822.461</t>
+          <t>4822461000.00052</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4701.229</t>
+          <t>4701228999.9987</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>4740.226</t>
+          <t>4740226000.00008</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4833.121</t>
+          <t>4833121000.0005</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>4904.024</t>
+          <t>4904023999.99952</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>4975.564</t>
+          <t>4975563999.99954</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>4572.334</t>
+          <t>4572333999.99951</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>4645.949</t>
+          <t>4645949000.00006</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>4654.643</t>
+          <t>4654642999.99877</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>4702.879</t>
+          <t>4702879000.00026</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>4685.242</t>
+          <t>4685242000.00107</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>4515.742</t>
+          <t>4515742174.43629</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>4536.368</t>
+          <t>4536367757.16935</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>4532.435</t>
+          <t>4532434968.90499</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>4573.943</t>
+          <t>4573942537.44066</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4587.027</t>
+          <t>4587027470.24489</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>4849.614</t>
+          <t>4849613582.63034</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>4659.659</t>
+          <t>4659658596.42348</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>4713.53</t>
+          <t>4713530011.11967</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>36770.617</t>
+          <t>36770616983.2729</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>34258.1</t>
+          <t>34258099999.9955</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38263.1</t>
+          <t>38263100000.0016</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>38329.5</t>
+          <t>38329500000.0053</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>31156.3</t>
+          <t>31156299999.9989</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>39345.1</t>
+          <t>39345100000.0036</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>39400</t>
+          <t>39399999999.9995</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>39732.8</t>
+          <t>39732800000.0047</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>38909.7</t>
+          <t>38909700000.0069</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>38833.6</t>
+          <t>38833600000.0106</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>39640.2</t>
+          <t>39640200000.0058</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>39763.3</t>
+          <t>39763299999.988</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>39573.4</t>
+          <t>39573400000.0008</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>40570.5</t>
+          <t>40570500000.0104</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>40946.5</t>
+          <t>40946500000.0035</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>39994.7</t>
+          <t>39994700000.0079</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>40149.8</t>
+          <t>40149799999.9911</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>40492.2</t>
+          <t>40492200000.0046</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>40346.2</t>
+          <t>40346200000.0122</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>38672.958</t>
+          <t>38672958101.9843</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>38802.193</t>
+          <t>38802192935.533</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>38759.309</t>
+          <t>38759309221.1831</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>37956.396</t>
+          <t>37956395935.8891</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>36440.482</t>
+          <t>36440481782.7108</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>37662.401</t>
+          <t>37662401396.7564</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>37775.695</t>
+          <t>37775695380.7503</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>37345.852</t>
+          <t>37345852399.8449</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>64338.853</t>
+          <t>64338853334.664</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>51110.523</t>
+          <t>51110522999.9962</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>52469.462</t>
+          <t>52469461999.9964</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>53126.984</t>
+          <t>53126984000.0053</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>53682.609</t>
+          <t>53682609000.0004</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>53182.798</t>
+          <t>53182797999.9932</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>53711.414</t>
+          <t>53711414000.0004</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>51806.621</t>
+          <t>51806621000.0002</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>54643.964</t>
+          <t>54643963999.9988</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>54670.285</t>
+          <t>54670284999.9993</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>54997.096</t>
+          <t>54997096000.012</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>56155.65</t>
+          <t>56155650000.0008</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>56617.615</t>
+          <t>56617614999.9909</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>57091.34</t>
+          <t>57091339999.9999</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>54503.353</t>
+          <t>54503352999.9986</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>53203.327</t>
+          <t>53203326999.9902</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>53017.461</t>
+          <t>53017460999.9973</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>53294.088</t>
+          <t>53294088000.0026</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>54076.166</t>
+          <t>54076166000.0024</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>53579.534</t>
+          <t>53579534032.4765</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>58359.739</t>
+          <t>58359739451.5685</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>67201.087</t>
+          <t>67201087170.9512</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>59658.557</t>
+          <t>59658556993.1228</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>57601.589</t>
+          <t>57601588846.2819</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>60309.588</t>
+          <t>60309587862.6613</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>62861.23</t>
+          <t>62861230107.6549</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>63334.933</t>
+          <t>63334932694.5987</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>7662.504</t>
+          <t>7662504185.98153</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8616.147</t>
+          <t>8616146999.99837</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8629.81</t>
+          <t>8629810000.00012</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>8581.28</t>
+          <t>8581279999.9982</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8977.125</t>
+          <t>8977125000.0017</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>9123.421</t>
+          <t>9123421000.00045</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>9179.603</t>
+          <t>9179602999.99891</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>9195.814</t>
+          <t>9195813999.99754</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>9333.985</t>
+          <t>9333985000.00123</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9588.609</t>
+          <t>9588608999.99924</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9668.449</t>
+          <t>9668449000.00069</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9699.362</t>
+          <t>9699361999.99989</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>9800.217</t>
+          <t>9800216999.99885</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>9849.725</t>
+          <t>9849725000.0039</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9805.815</t>
+          <t>9805814999.99804</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>9587.005</t>
+          <t>9587005000.00074</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>9376.645</t>
+          <t>9376645000.00135</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>8737.796</t>
+          <t>8737796000.00036</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>8021.353</t>
+          <t>8021352999.99865</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>7513.78</t>
+          <t>7513779761.8819</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>7130.833</t>
+          <t>7130833315.91656</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>7123.238</t>
+          <t>7123237969.22613</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>6775.317</t>
+          <t>6775317391.62617</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7053.37</t>
+          <t>7053369542.70599</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>7108.471</t>
+          <t>7108470579.69951</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>7258.284</t>
+          <t>7258284321.42807</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>7311.421</t>
+          <t>7311421357.19344</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>9311.948</t>
+          <t>9311948372.18986</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>8185.946</t>
+          <t>8185946000.00026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7983.327</t>
+          <t>7983326999.99981</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>8036.327</t>
+          <t>8036327000.00058</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>8085.717</t>
+          <t>8085716999.99872</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>8454.505</t>
+          <t>8454505000.0001</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8164.336</t>
+          <t>8164335999.9993</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8547.169</t>
+          <t>8547169000.00011</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8192.971</t>
+          <t>8192970999.99851</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8569.793</t>
+          <t>8569792999.99942</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>8503.135</t>
+          <t>8503134999.9988</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>8269.235</t>
+          <t>8269235000.0008</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>8475.125</t>
+          <t>8475124999.99996</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>8401.981</t>
+          <t>8401981000.00053</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>7955.018</t>
+          <t>7955017999.99904</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>7829.646</t>
+          <t>7829646000.00033</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>7816.867</t>
+          <t>7816866999.99999</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>7802.694</t>
+          <t>7802694000.00073</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>7820.09</t>
+          <t>7820089999.99894</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>7642.752</t>
+          <t>7642751941.05801</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>7644.57</t>
+          <t>7644569589.98377</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>8060.176</t>
+          <t>8060175804.30992</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>7959.893</t>
+          <t>7959892867.19085</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>8556.384</t>
+          <t>8556383992.18949</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>9133.616</t>
+          <t>9133615735.06327</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>9462.556</t>
+          <t>9462555936.28276</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>9670.951</t>
+          <t>9670950888.0564</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2171833.039</t>
+          <t>2171833039490.27</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>818402.313</t>
+          <t>818402313000.033</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>844057.515</t>
+          <t>844057515000.015</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>843181.748</t>
+          <t>843181748000.152</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>824584.604</t>
+          <t>824584604000.182</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>851441.141</t>
+          <t>851441140999.95</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>906000.225</t>
+          <t>906000224999.802</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>899003.887</t>
+          <t>899003886999.949</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>880933.995</t>
+          <t>880933995000.16</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>894204.418</t>
+          <t>894204418000.016</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>897202.015</t>
+          <t>897202014999.877</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>896040.133</t>
+          <t>896040133000.049</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>892578.846</t>
+          <t>892578845999.921</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>894320.887</t>
+          <t>894320886999.811</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>895341</t>
+          <t>895340999999.962</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>897249.373</t>
+          <t>897249373000.143</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>896914.317</t>
+          <t>896914317000.024</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>904368.491</t>
+          <t>904368491000.193</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>909727.741</t>
+          <t>909727741000.242</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>895207.269</t>
+          <t>895207269406.163</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>944959.6</t>
+          <t>944959599879.792</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1162575.356</t>
+          <t>1162575356154.66</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1244363.792</t>
+          <t>1244363792448.83</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1393024.021</t>
+          <t>1393024021254.7</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1389941.183</t>
+          <t>1389941183177.29</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1536396.459</t>
+          <t>1536396458761.45</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1644821.873</t>
+          <t>1644821873447.36</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>400443.019</t>
+          <t>400443019322.474</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>159748.684</t>
+          <t>159748684000.038</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>171293.068</t>
+          <t>171293068000.021</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>175564.396</t>
+          <t>175564395999.99</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>174715.623</t>
+          <t>174715622999.979</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>177777.422</t>
+          <t>177777421999.999</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>170126.99</t>
+          <t>170126989999.989</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>183341.336</t>
+          <t>183341335999.988</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>179586.988</t>
+          <t>179586987999.981</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>182376.093</t>
+          <t>182376093000.008</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>198460.272</t>
+          <t>198460271999.985</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>193845.386</t>
+          <t>193845385999.993</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>201335.393</t>
+          <t>201335393000.016</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>211094.576</t>
+          <t>211094576000.11</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>222632.673</t>
+          <t>222632673000.011</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>219844.436</t>
+          <t>219844436000.05</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>228328.637</t>
+          <t>228328637000.004</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>221567.196</t>
+          <t>221567196000.042</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>238960.696</t>
+          <t>238960695999.902</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>234290.15</t>
+          <t>234290150475.847</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>224315.049</t>
+          <t>224315049315.831</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>276364.455</t>
+          <t>276364455487.317</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>293791.174</t>
+          <t>293791173590.185</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>263959.634</t>
+          <t>263959634319.968</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>257941.521</t>
+          <t>257941521206.767</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>286545.049</t>
+          <t>286545049389.112</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>301526.123</t>
+          <t>301526122675.271</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6740.67</t>
+          <t>6740669730.12152</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2467.074</t>
+          <t>2467074000.00028</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2701.785</t>
+          <t>2701784999.99984</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2818.018</t>
+          <t>2818018000.00005</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2909.62</t>
+          <t>2909619999.99953</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3221.355</t>
+          <t>3221355000.00074</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3350.649</t>
+          <t>3350648999.99979</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3437.317</t>
+          <t>3437316999.99909</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>3405.903</t>
+          <t>3405902999.99969</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3482.123</t>
+          <t>3482122999.99943</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>3537.096</t>
+          <t>3537095999.99993</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>3776.972</t>
+          <t>3776972000.00107</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>3934.234</t>
+          <t>3934233999.99976</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>4047.793</t>
+          <t>4047793000.00009</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>3963.095</t>
+          <t>3963095000.00046</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>3440.41</t>
+          <t>3440410000.00041</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>3414.197</t>
+          <t>3414197000.00028</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>3352.109</t>
+          <t>3352108999.99956</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>3178.049</t>
+          <t>3178048999.99924</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>3442.42</t>
+          <t>3442419646.67317</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>3597.922</t>
+          <t>3597922239.81212</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>4595.324</t>
+          <t>4595324465.87109</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>5098.67</t>
+          <t>5098669801.95822</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>5204.554</t>
+          <t>5204553525.31393</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>5415.836</t>
+          <t>5415835869.96329</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>6004.651</t>
+          <t>6004651096.48624</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>6388.714</t>
+          <t>6388714451.43984</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>44239.139</t>
+          <t>44239138748.0209</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>42277.24</t>
+          <t>42277239999.999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>41883.317</t>
+          <t>41883316999.9999</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>42668.851</t>
+          <t>42668851000.0019</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>43000.464</t>
+          <t>43000463999.9966</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>43355.111</t>
+          <t>43355111000.0039</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>43933.948</t>
+          <t>43933947999.9914</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>44982.249</t>
+          <t>44982249000.0018</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>41719.222</t>
+          <t>41719221999.9942</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>46023.217</t>
+          <t>46023216999.9928</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>46274.049</t>
+          <t>46274049000.0006</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>46083.019</t>
+          <t>46083018999.9993</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>46725.658</t>
+          <t>46725658000.0113</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>47175.487</t>
+          <t>47175487000.0046</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>45906.791</t>
+          <t>45906790999.9975</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>44663.348</t>
+          <t>44663348000.0014</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>44485.91</t>
+          <t>44485909999.9937</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>44335.815</t>
+          <t>44335814999.9857</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>43414.7</t>
+          <t>43414699999.9994</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>41989.162</t>
+          <t>41989161562.2158</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>41919.036</t>
+          <t>41919035992.4415</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>42262.971</t>
+          <t>42262970778.6776</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>42506.737</t>
+          <t>42506737458.1</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>43062.898</t>
+          <t>43062898006.7977</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>44490.936</t>
+          <t>44490936433.3799</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>43708.756</t>
+          <t>43708756362.2667</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>44236.891</t>
+          <t>44236891369.6456</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>101440.282</t>
+          <t>101440282020.024</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>140587.261</t>
+          <t>140587261000.024</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>141113.841</t>
+          <t>141113841000.018</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>142519.138</t>
+          <t>142519137999.993</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>141360.688</t>
+          <t>141360688000.003</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>140220.689</t>
+          <t>140220689000.003</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>139912.613</t>
+          <t>139912612999.989</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>138925.01</t>
+          <t>138925010000.026</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>136864.824</t>
+          <t>136864823999.987</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>136296.395</t>
+          <t>136296394999.995</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>136155.834</t>
+          <t>136155834000.024</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>136440.812</t>
+          <t>136440811999.978</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>137208.122</t>
+          <t>137208121999.979</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>137628.494</t>
+          <t>137628494000.021</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>136904.573</t>
+          <t>136904573000.004</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>131598.74</t>
+          <t>131598740000</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>130974.376</t>
+          <t>130974376000.005</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>130488.098</t>
+          <t>130488097999.952</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>129563.512</t>
+          <t>129563512000.019</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>100569.273</t>
+          <t>100569273282.559</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>100026.584</t>
+          <t>100026583826.806</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>104167.667</t>
+          <t>104167667406.275</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>110588.624</t>
+          <t>110588623819.857</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>103124.536</t>
+          <t>103124536423.079</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>101881.747</t>
+          <t>101881747338.533</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>108273.336</t>
+          <t>108273335859.043</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>107412.313</t>
+          <t>107412313431.307</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>89129.146</t>
+          <t>89129146463.853</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48765.4</t>
+          <t>48765399999.9985</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>49780.583</t>
+          <t>49780583000.0033</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>50512.35</t>
+          <t>50512349999.9962</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>47655.703</t>
+          <t>47655703000.0089</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>48447.263</t>
+          <t>48447263000.0024</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>50678.971</t>
+          <t>50678971000.0163</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>51745.589</t>
+          <t>51745588999.9909</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>53168.73</t>
+          <t>53168730000.0079</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>53038.633</t>
+          <t>53038633000.0129</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>54153.754</t>
+          <t>54153753999.9919</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>54841.327</t>
+          <t>54841326999.9967</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>55521.003</t>
+          <t>55521002999.9991</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>55830.457</t>
+          <t>55830456999.9893</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>56633.551</t>
+          <t>56633550999.9937</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>56065.176</t>
+          <t>56065176000.0134</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>55898.407</t>
+          <t>55898407000.0023</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>56933.777</t>
+          <t>56933776999.9972</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>57958.028</t>
+          <t>57958028000.0101</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>55088.013</t>
+          <t>55088012997.7372</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>66462.233</t>
+          <t>66462233407.5278</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>78217.401</t>
+          <t>78217401206.6199</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>77777.735</t>
+          <t>77777734876.5221</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>80198.855</t>
+          <t>80198855272.0631</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>80376.95</t>
+          <t>80376950222.1345</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>80575.582</t>
+          <t>80575581910.1064</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>80601.278</t>
+          <t>80601277574.8873</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3924.144</t>
+          <t>3924143786.28414</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3380.531</t>
+          <t>3380531000.00017</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3369.506</t>
+          <t>3369505999.99852</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3390.363</t>
+          <t>3390362999.99981</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3395.361</t>
+          <t>3395360999.99956</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3336.095</t>
+          <t>3336095000.00038</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3103.155</t>
+          <t>3103154999.99957</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2918.134</t>
+          <t>2918133999.99955</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2973.117</t>
+          <t>2973116999.99912</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3011.863</t>
+          <t>3011863000.00026</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2912.496</t>
+          <t>2912495999.99974</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2984.164</t>
+          <t>2984163999.99912</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2973.36</t>
+          <t>2973359999.99886</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3063.689</t>
+          <t>3063689000.00028</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2956.109</t>
+          <t>2956109000.00011</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2688.184</t>
+          <t>2688184000.00018</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2539.975</t>
+          <t>2539974999.99962</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2537.07</t>
+          <t>2537069999.99991</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2573.434</t>
+          <t>2573434000.00055</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2617.923</t>
+          <t>2617922784.04929</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2692.881</t>
+          <t>2692880683.99598</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2768.474</t>
+          <t>2768473930.61529</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2835.501</t>
+          <t>2835500938.56604</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3064.371</t>
+          <t>3064370601.77711</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>3349.839</t>
+          <t>3349839050.95009</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3444.703</t>
+          <t>3444703435.36961</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3605.332</t>
+          <t>3605331542.37685</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>673.38</t>
+          <t>673379560.43965</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>329.4</t>
+          <t>329400000.00003</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>333.636</t>
+          <t>333635999.999947</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>336.768</t>
+          <t>336767999.999921</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>332.075</t>
+          <t>332075000.000028</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>345.225</t>
+          <t>345225000.00007</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>355.881</t>
+          <t>355881000.00006</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>367.319</t>
+          <t>367319000.000039</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>367.088</t>
+          <t>367088000.000056</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>357.904</t>
+          <t>357903999.999912</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>360.534</t>
+          <t>360534000.000107</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>367.97</t>
+          <t>367969999.999883</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>376.505</t>
+          <t>376504999.999984</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>381.132</t>
+          <t>381132000.000021</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>370.782</t>
+          <t>370781999.999988</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>392.508</t>
+          <t>392508000.000017</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>388.349</t>
+          <t>388349000.000082</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>402.13</t>
+          <t>402130000.000187</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>430.305</t>
+          <t>430305000.00005</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>450.901</t>
+          <t>450901395.665593</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>517.424</t>
+          <t>517424076.01036</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>543.543</t>
+          <t>543542830.199463</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>561.712</t>
+          <t>561712055.741051</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>563.358</t>
+          <t>563358062.936238</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>577.669</t>
+          <t>577669143.218786</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>609.491</t>
+          <t>609490883.155899</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>628.397</t>
+          <t>628396783.026773</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2795.286</t>
+          <t>2795286475.21463</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2321.361</t>
+          <t>2321361000.00083</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2355.422</t>
+          <t>2355422000.00023</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2319.763</t>
+          <t>2319762999.99983</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2171.498</t>
+          <t>2171498000.00042</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2289.441</t>
+          <t>2289440999.99968</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2215.011</t>
+          <t>2215011000.00013</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2286.728</t>
+          <t>2286727999.99985</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2331.579</t>
+          <t>2331579000.00038</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2355.983</t>
+          <t>2355982999.99966</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2344.863</t>
+          <t>2344862999.99993</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2371.724</t>
+          <t>2371724000.00041</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2501.374</t>
+          <t>2501374000.00012</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2324.75</t>
+          <t>2324750000.00022</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2214.72</t>
+          <t>2214720000.00059</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1870.716</t>
+          <t>1870716000.0002</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1727.862</t>
+          <t>1727861999.99982</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1632.157</t>
+          <t>1632157000.00004</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1739.721</t>
+          <t>1739721000.00004</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1894.692</t>
+          <t>1894692481.38113</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>1792.556</t>
+          <t>1792555514.90341</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2012.28</t>
+          <t>2012280462.98664</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1907.56</t>
+          <t>1907559647.68816</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>2169.817</t>
+          <t>2169817151.03983</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2309.447</t>
+          <t>2309446869.61626</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2275.276</t>
+          <t>2275275692.9776</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2356.7</t>
+          <t>2356700127.12889</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>166944.645</t>
+          <t>166944645218.944</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>73030.156</t>
+          <t>73030155999.9829</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>78639.907</t>
+          <t>78639907000.0012</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>83734.201</t>
+          <t>83734200999.999</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>84392.359</t>
+          <t>84392359000.003</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>86949.92</t>
+          <t>86949920000.0032</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>86773.862</t>
+          <t>86773861999.9959</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>85949.043</t>
+          <t>85949042999.9945</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>89434.235</t>
+          <t>89434234999.9895</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>88114.403</t>
+          <t>88114403000.0022</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>91242.593</t>
+          <t>91242593000.0253</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>91776.679</t>
+          <t>91776679000.02</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>94921.542</t>
+          <t>94921541999.9694</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>96536.335</t>
+          <t>96536334999.9932</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>101615.166</t>
+          <t>101615165999.976</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>103685.902</t>
+          <t>103685901999.992</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>106272.579</t>
+          <t>106272579000.015</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>107328.261</t>
+          <t>107328260999.988</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>111338.223</t>
+          <t>111338222999.983</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>116332.785</t>
+          <t>116332785379.224</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>132673.529</t>
+          <t>132673528934.628</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>126267.684</t>
+          <t>126267684168.211</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>111749.052</t>
+          <t>111749052297.274</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>129687.637</t>
+          <t>129687636926.603</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>132697.752</t>
+          <t>132697752132.336</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>145760.456</t>
+          <t>145760456153.465</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>149205.754</t>
+          <t>149205753836.131</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>676.167</t>
+          <t>676166990.510132</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>281.998</t>
+          <t>281997999.999983</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>308.282</t>
+          <t>308282000.00002</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>316.509</t>
+          <t>316509000.000068</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>321.324</t>
+          <t>321324000.000028</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>325.855</t>
+          <t>325854999.999998</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>328.684</t>
+          <t>328683999.999948</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>283.89</t>
+          <t>283890000.00003</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>324.922</t>
+          <t>324922000.000075</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>316.179</t>
+          <t>316179000.000005</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>324.689</t>
+          <t>324688999.999989</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>316.238</t>
+          <t>316237999.999992</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>310.265</t>
+          <t>310265000.000007</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>332.955</t>
+          <t>332954999.999948</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>325.723</t>
+          <t>325723000.000043</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>324.413</t>
+          <t>324413000.000041</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>326.249</t>
+          <t>326248999.999981</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>329.467</t>
+          <t>329466999.999935</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>336.029</t>
+          <t>336029000.000037</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>368.103</t>
+          <t>368103000.349586</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>416.145</t>
+          <t>416145190.894236</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>453.925</t>
+          <t>453925476.673435</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>482.646</t>
+          <t>482645926.570051</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>534.919</t>
+          <t>534919484.901472</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>607.575</t>
+          <t>607574596.213217</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>640.913</t>
+          <t>640912695.594709</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>660.693</t>
+          <t>660693479.330843</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>14852.575</t>
+          <t>14852575410.2174</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>11133.426</t>
+          <t>11133426000.001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11959.601</t>
+          <t>11959601000.0005</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>12299.631</t>
+          <t>12299630999.9997</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>12760.614</t>
+          <t>12760614000.0018</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12934.605</t>
+          <t>12934604999.9978</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12868.342</t>
+          <t>12868342000.0003</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>13374.452</t>
+          <t>13374451999.9977</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>12545.298</t>
+          <t>12545297999.9998</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>13312.965</t>
+          <t>13312965000.0003</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>12999.435</t>
+          <t>12999435000.0018</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>13483.77</t>
+          <t>13483769999.999</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>13913.697</t>
+          <t>13913697000.0014</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>14286.945</t>
+          <t>14286945000.0002</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>13548.049</t>
+          <t>13548049000.0053</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>13081.378</t>
+          <t>13081377999.9999</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>12511.437</t>
+          <t>12511436999.9978</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>12410.031</t>
+          <t>12410030999.9974</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>12543.872</t>
+          <t>12543871999.9982</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>12127.138</t>
+          <t>12127137730.2632</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>12235.599</t>
+          <t>12235598878.1007</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>12059.68</t>
+          <t>12059679840.5622</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>11970.243</t>
+          <t>11970242553.8239</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12360.951</t>
+          <t>12360950698.5746</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>12505.993</t>
+          <t>12505992816.4665</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12680.728</t>
+          <t>12680727738.8102</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>12691.308</t>
+          <t>12691307988.6382</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>43271.418</t>
+          <t>43271417699.8908</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>33034.413</t>
+          <t>33034412999.9904</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>33512.747</t>
+          <t>33512747000.0012</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>33263.358</t>
+          <t>33263357999.9992</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>33013.293</t>
+          <t>33013293000.0023</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>32312.381</t>
+          <t>32312381000.0046</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>32514.121</t>
+          <t>32514120999.994</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>31494.078</t>
+          <t>31494077999.9953</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>30762.742</t>
+          <t>30762741999.9961</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>30262.805</t>
+          <t>30262805000.0019</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>30450.534</t>
+          <t>30450533999.9963</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>31047.637</t>
+          <t>31047636999.9986</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>32115.523</t>
+          <t>32115523000.0095</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>33532.989</t>
+          <t>33532988999.9889</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>33632.068</t>
+          <t>33632068000.0038</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>33407.807</t>
+          <t>33407806999.9944</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>32532.887</t>
+          <t>32532887000.0099</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>32565.839</t>
+          <t>32565839000.0044</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>32633.862</t>
+          <t>32633861999.9983</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>32331.849</t>
+          <t>32331849071.6698</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>32443.997</t>
+          <t>32443997017.7018</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>33333.506</t>
+          <t>33333505860.4451</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>32285.007</t>
+          <t>32285007436.9303</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>35648.644</t>
+          <t>35648644424.0861</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>36205.586</t>
+          <t>36205585659.0533</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>38880.452</t>
+          <t>38880452247.4661</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>40484.612</t>
+          <t>40484611922.2429</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10443.975</t>
+          <t>10443974928.2431</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>9849.452</t>
+          <t>9849451999.99968</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>9659.319</t>
+          <t>9659319000.00126</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9652.003</t>
+          <t>9652002999.99918</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10258.29</t>
+          <t>10258290000.0012</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>10375.261</t>
+          <t>10375260999.9998</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10349.377</t>
+          <t>10349376999.9989</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>10578.772</t>
+          <t>10578772000</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>10615.527</t>
+          <t>10615526999.9978</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>10328.799</t>
+          <t>10328798999.9999</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>10617.514</t>
+          <t>10617514000.0006</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>10517.311</t>
+          <t>10517311000.0023</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>10557.791</t>
+          <t>10557790999.9984</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>10503.638</t>
+          <t>10503638000.0006</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>10410.561</t>
+          <t>10410561000.0003</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>10133.911</t>
+          <t>10133911000.0009</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>9998.044</t>
+          <t>9998043999.99715</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>9680.563</t>
+          <t>9680563000.0021</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>9245.295</t>
+          <t>9245295000.00036</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>9173.806</t>
+          <t>9173806026.24451</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>9132.209</t>
+          <t>9132209154.05445</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>9246.132</t>
+          <t>9246131932.82745</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>9359.829</t>
+          <t>9359829443.56343</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9886.645</t>
+          <t>9886644999.19202</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>10133.554</t>
+          <t>10133554339.6512</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10284.518</t>
+          <t>10284518143.405</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>10393.441</t>
+          <t>10393441257.0838</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>31377.358</t>
+          <t>31377358376.5468</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20391.205</t>
+          <t>20391204999.9925</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20364.145</t>
+          <t>20364144999.9962</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>23212.665</t>
+          <t>23212665000.0018</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23250.058</t>
+          <t>23250057999.9947</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>22980.662</t>
+          <t>22980661999.9986</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>22829.129</t>
+          <t>22829128999.9985</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>21820.325</t>
+          <t>21820325000.0014</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>20110.784</t>
+          <t>20110784000.0013</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>19243.603</t>
+          <t>19243603000.0036</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>19788.84</t>
+          <t>19788840000.0002</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>18530.393</t>
+          <t>18530392999.9988</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>19331.072</t>
+          <t>19331072000.0008</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>19467.463</t>
+          <t>19467462999.9979</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>19125.764</t>
+          <t>19125764000.0052</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>18785.43</t>
+          <t>18785430000</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>17620.586</t>
+          <t>17620585999.9983</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>17323.222</t>
+          <t>17323222000</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>17795.596</t>
+          <t>17795596000.0016</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>20055.695</t>
+          <t>20055694560.121</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>20156.896</t>
+          <t>20156895944.0141</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>22117.16</t>
+          <t>22117159789.654</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>22979.544</t>
+          <t>22979544036.7834</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>27027.047</t>
+          <t>27027047342.927</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>29355.007</t>
+          <t>29355006682.1283</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>29727.328</t>
+          <t>29727327535.6592</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>29871.476</t>
+          <t>29871475574.8814</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>133596.86</t>
+          <t>133596859953.673</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>115795.261</t>
+          <t>115795261000.013</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>116025.048</t>
+          <t>116025048000.012</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>115261.266</t>
+          <t>115261266000.014</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>113918.698</t>
+          <t>113918697999.995</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>122096.354</t>
+          <t>122096353999.996</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>126353.905</t>
+          <t>126353905000.005</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>127011.144</t>
+          <t>127011144000.025</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>130152.309</t>
+          <t>130152309000.035</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>130040.446</t>
+          <t>130040445999.987</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>122555.317</t>
+          <t>122555316999.988</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>133616.965</t>
+          <t>133616964999.982</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>134998.125</t>
+          <t>134998125000.002</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>138570.733</t>
+          <t>138570732999.99</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>131892.914</t>
+          <t>131892914000.025</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>136096.775</t>
+          <t>136096775000.012</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>138156.604</t>
+          <t>138156604000.006</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>128580.35</t>
+          <t>128580349999.996</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>141511.214</t>
+          <t>141511214000.038</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>144139.741</t>
+          <t>144139741245.498</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>125727.187</t>
+          <t>125727186696.913</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>101139.112</t>
+          <t>101139111524.291</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>95055.001</t>
+          <t>95055000803.0034</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>113851.361</t>
+          <t>113851361375.712</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>112698.467</t>
+          <t>112698467077.717</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>121659.064</t>
+          <t>121659063746.742</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>123886.883</t>
+          <t>123886882741.023</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6331.051</t>
+          <t>6331050955.80502</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4908.361</t>
+          <t>4908361000.0008</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5076.616</t>
+          <t>5076616000.00021</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>5064.473</t>
+          <t>5064473000.00012</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4925.064</t>
+          <t>4925063999.99941</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4863.195</t>
+          <t>4863194999.9992</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>4718.968</t>
+          <t>4718968000.00049</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4642.952</t>
+          <t>4642951999.99997</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4664.118</t>
+          <t>4664117999.99938</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>4752.209</t>
+          <t>4752209000.00168</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4718.144</t>
+          <t>4718143999.99992</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>4898.591</t>
+          <t>4898590999.99925</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>4898.066</t>
+          <t>4898065999.99966</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5121.643</t>
+          <t>5121643000.00025</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>4948.559</t>
+          <t>4948558999.99906</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>4826.991</t>
+          <t>4826990999.99898</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>4754.817</t>
+          <t>4754816999.99936</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>4761.002</t>
+          <t>4761001999.9986</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>4770.787</t>
+          <t>4770786999.99976</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>4695.304</t>
+          <t>4695304433.36828</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>4760.553</t>
+          <t>4760553339.33451</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>4994.777</t>
+          <t>4994776697.6024</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>4844.226</t>
+          <t>4844226311.65836</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>5195.624</t>
+          <t>5195623690.75272</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>5253.491</t>
+          <t>5253490749.89922</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>5422.07</t>
+          <t>5422069675.11295</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>5742.24</t>
+          <t>5742240345.23911</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2232.146</t>
+          <t>2232145630.96959</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2018.98</t>
+          <t>2018980000.00052</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1996.752</t>
+          <t>1996752000.00013</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1956.224</t>
+          <t>1956223999.99966</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1979.159</t>
+          <t>1979158999.9998</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1982.423</t>
+          <t>1982422999.99998</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1976.89</t>
+          <t>1976890000.00036</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1969.298</t>
+          <t>1969298000.00018</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2009.123</t>
+          <t>2009122999.99995</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1937.166</t>
+          <t>1937166000.00002</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2020.152</t>
+          <t>2020152000.00012</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2062.407</t>
+          <t>2062407000.00022</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2053.903</t>
+          <t>2053903000.00008</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2105.927</t>
+          <t>2105926999.99977</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2066.279</t>
+          <t>2066278999.99985</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1999.6</t>
+          <t>1999600000.00011</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1959.744</t>
+          <t>1959743999.99966</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1885.166</t>
+          <t>1885166000.00019</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1865.533</t>
+          <t>1865532999.99996</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1831.86</t>
+          <t>1831860058.12441</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>1796.069</t>
+          <t>1796069209.74435</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>1867.298</t>
+          <t>1867297877.08137</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>1845.664</t>
+          <t>1845664409.77999</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1915.773</t>
+          <t>1915772811.10684</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2034.112</t>
+          <t>2034112412.62926</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2103.568</t>
+          <t>2103567832.18129</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>2220.648</t>
+          <t>2220647798.48616</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7598.077</t>
+          <t>7598077022.19168</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7501.044</t>
+          <t>7501043999.9998</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7472.931</t>
+          <t>7472930999.99861</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7766.793</t>
+          <t>7766792999.99893</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>7247.423</t>
+          <t>7247423000.00048</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8082.817</t>
+          <t>8082817000.00206</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>8273.316</t>
+          <t>8273316000.0015</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>8179.094</t>
+          <t>8179094000.00069</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8281.619</t>
+          <t>8281618999.99972</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>8089.403</t>
+          <t>8089403000.00036</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>8116.307</t>
+          <t>8116306999.99939</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>8426.406</t>
+          <t>8426405999.99876</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>8579.604</t>
+          <t>8579603999.99801</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>8780.299</t>
+          <t>8780299000.00047</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>8571.183</t>
+          <t>8571183000.00138</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>8306.362</t>
+          <t>8306362000.00134</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>8504.72</t>
+          <t>8504720000.0037</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>8661.381</t>
+          <t>8661381000.00022</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>8678.845</t>
+          <t>8678845000.00138</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>8673.975</t>
+          <t>8673974808.99018</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>8234.389</t>
+          <t>8234388899.31017</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>8312.344</t>
+          <t>8312343904.74769</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>8053.287</t>
+          <t>8053286863.69826</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>8065.106</t>
+          <t>8065106327.83316</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>8026.416</t>
+          <t>8026416027.92743</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>7941.661</t>
+          <t>7941661193.69262</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>7590.201</t>
+          <t>7590200748.00271</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>72019.181</t>
+          <t>72019181052.972</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>46852.384</t>
+          <t>46852384000.0098</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>48030.768</t>
+          <t>48030768000.0083</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>48359.994</t>
+          <t>48359993999.9976</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>49575.55</t>
+          <t>49575550000.0098</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>50716.349</t>
+          <t>50716348999.9947</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>52229.132</t>
+          <t>52229132000.0077</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>54444.554</t>
+          <t>54444553999.9951</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>54135.707</t>
+          <t>54135707000.0118</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>53545.698</t>
+          <t>53545697999.9976</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>55833.248</t>
+          <t>55833247999.9837</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>59372.597</t>
+          <t>59372597000.0011</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>55112.822</t>
+          <t>55112822000.008</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>53512.02</t>
+          <t>53512019999.9925</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>55256.652</t>
+          <t>55256651999.9951</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>53701.25</t>
+          <t>53701250000.0083</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>55832.97</t>
+          <t>55832969999.9978</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>59143.827</t>
+          <t>59143826999.9862</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>61914.777</t>
+          <t>61914776999.9911</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>62781.656</t>
+          <t>62781655630.7099</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>60010.983</t>
+          <t>60010982570.6192</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>67361.218</t>
+          <t>67361218305.7574</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>65871.389</t>
+          <t>65871389148.0098</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>62634.648</t>
+          <t>62634648393.5121</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>54985.97</t>
+          <t>54985969939.7044</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>56407.236</t>
+          <t>56407236288.7252</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>59530.308</t>
+          <t>59530307947.6011</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>30923.318</t>
+          <t>30923317559.3836</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>21349.979</t>
+          <t>21349978519.9956</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>21875.572</t>
+          <t>21875572159.9982</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>21831.93</t>
+          <t>21831930120.0037</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20873.63</t>
+          <t>20873629919.9972</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>19691.231</t>
+          <t>19691230519.9955</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20833.696</t>
+          <t>20833696000.0013</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>18437.834</t>
+          <t>18437833960.0038</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19363.382</t>
+          <t>19363382480.0036</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>20515.082</t>
+          <t>20515081599.9971</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>21075.76</t>
+          <t>21075760159.9942</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>20870.053</t>
+          <t>20870052839.9952</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>21768.6</t>
+          <t>21768600360.0037</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>21628.44</t>
+          <t>21628440080.0004</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>21489.457</t>
+          <t>21489456560.0043</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>21955.43</t>
+          <t>21955429599.9976</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>21610.171</t>
+          <t>21610171439.997</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>22882.791</t>
+          <t>22882791360.0062</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>23201.57</t>
+          <t>23201569560.0004</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>22883.197</t>
+          <t>22883196905.3845</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>23094.788</t>
+          <t>23094788338.7557</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>26403.188</t>
+          <t>26403187985.8109</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>26190.337</t>
+          <t>26190337351.4304</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>28138.035</t>
+          <t>28138034845.0882</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>28164.847</t>
+          <t>28164847143.1681</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>29401.468</t>
+          <t>29401467595.118</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>29432.569</t>
+          <t>29432569199.6184</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>350066.377</t>
+          <t>350066376996.465</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>231678.3</t>
+          <t>231678300000.018</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>235382.6</t>
+          <t>235382599999.989</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>218699.3</t>
+          <t>218699300000.015</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>244915.7</t>
+          <t>244915699999.989</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>248202.2</t>
+          <t>248202200000.004</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>250068.2</t>
+          <t>250068200000.006</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>247322.8</t>
+          <t>247322800000.042</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>244650.5</t>
+          <t>244650500000.043</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>218699.6</t>
+          <t>218699599999.943</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>246757.1</t>
+          <t>246757100000.072</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>223473.1</t>
+          <t>223473099999.994</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>254734.9</t>
+          <t>254734899999.972</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>256939</t>
+          <t>256938999999.924</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>254869</t>
+          <t>254869000000.041</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>241116.6</t>
+          <t>241116600000.014</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>240628.4</t>
+          <t>240628400000.034</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>213552.3</t>
+          <t>213552299999.961</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>248582.3</t>
+          <t>248582299999.962</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>243602.766</t>
+          <t>243602765739.691</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>249572.392</t>
+          <t>249572391606.034</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>314254.632</t>
+          <t>314254631544.766</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>314360.92</t>
+          <t>314360920483.009</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>323303.057</t>
+          <t>323303056844.291</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>314472.142</t>
+          <t>314472142191.779</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>349426.941</t>
+          <t>349426941315.954</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>350740.402</t>
+          <t>350740402065.107</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>11000657.389</t>
+          <t>11000657388748.8</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5232651.458</t>
+          <t>5232651458400.1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5333773.702</t>
+          <t>5333773701840.16</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5386235.29</t>
+          <t>5386235290359.54</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5459557.684</t>
+          <t>5459557684239.9</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5554913.631</t>
+          <t>5554913631320.39</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5631652.78</t>
+          <t>5631652779612.69</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>5709485.457</t>
+          <t>5709485456839.75</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>5783239.12</t>
+          <t>5783239120360.65</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5840760.727</t>
+          <t>5840760727280.46</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>5963892.532</t>
+          <t>5963892532439.7</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>6091927.764</t>
+          <t>6091927764000.48</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>6206653.288</t>
+          <t>6206653288239.95</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>6339773.926</t>
+          <t>6339773926320.28</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>6312404.542</t>
+          <t>6312404541799.85</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>6321974.889</t>
+          <t>6321974889040.39</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>6493726.574</t>
+          <t>6493726573759.86</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>6537703.842</t>
+          <t>6537703841800.28</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>6647957.989</t>
+          <t>6647957989080.08</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>6678508.4</t>
+          <t>6678508400355.47</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>6782760.549</t>
+          <t>6782760548942.46</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>7654694.296</t>
+          <t>7654694295913.99</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>7630963.816</t>
+          <t>7630963815666.89</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>8072181.981</t>
+          <t>8072181981344.58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>8128137.498</t>
+          <t>8128137498352.54</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>8827988.904</t>
+          <t>8827988904486.81</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>9176606.758</t>
+          <t>9176606757764.98</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3636.732</t>
+          <t>3636731513.05804</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3275.633</t>
+          <t>3275632999.99976</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3301.569</t>
+          <t>3301568999.99992</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>3314.102</t>
+          <t>3314102000.00005</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3413.668</t>
+          <t>3413667999.99969</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3213.14</t>
+          <t>3213139999.99928</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3441.038</t>
+          <t>3441038000.00016</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3255.942</t>
+          <t>3255942000.0004</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>3328.591</t>
+          <t>3328590999.99974</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>3382.951</t>
+          <t>3382951000.00155</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>3469.005</t>
+          <t>3469005000.00029</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>3409.757</t>
+          <t>3409756999.99995</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>3415.917</t>
+          <t>3415916999.99948</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>3500.428</t>
+          <t>3500428000.00041</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>3391.451</t>
+          <t>3391451000.00007</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>3308.779</t>
+          <t>3308778999.99975</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>3157.4</t>
+          <t>3157399999.99946</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>3041.67</t>
+          <t>3041669999.99932</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2938.848</t>
+          <t>2938847999.99973</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2951.8</t>
+          <t>2951799566.27507</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>2925.911</t>
+          <t>2925910662.16328</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2913.721</t>
+          <t>2913721492.70831</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>3101.362</t>
+          <t>3101361865.74348</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3064.751</t>
+          <t>3064751073.24278</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>3293.188</t>
+          <t>3293187605.81069</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>3344.912</t>
+          <t>3344911924.98342</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>3482.664</t>
+          <t>3482664249.46225</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>8461.804</t>
+          <t>8461803744.45548</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>7119.702</t>
+          <t>7119702000.00133</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6442.48</t>
+          <t>6442480000.00135</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>7080.755</t>
+          <t>7080755000.00196</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>7146.634</t>
+          <t>7146633999.9991</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6600.072</t>
+          <t>6600072000.00114</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>6613.249</t>
+          <t>6613248999.99974</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>6974.77</t>
+          <t>6974769999.99841</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>6825.583</t>
+          <t>6825582999.99983</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>7692.919</t>
+          <t>7692919000.00216</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>6926.7</t>
+          <t>6926699999.99987</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>6948.99</t>
+          <t>6948990000.00082</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>7086.695</t>
+          <t>7086694999.9995</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>7973.343</t>
+          <t>7973343000.00024</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>6846.695</t>
+          <t>6846694999.99923</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>7817.464</t>
+          <t>7817463999.9998</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>7042.354</t>
+          <t>7042354000.001</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>8100.009</t>
+          <t>8100009000.0004</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>8186.731</t>
+          <t>8186731000.00063</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>8228.331</t>
+          <t>8228331068.08972</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>7895.484</t>
+          <t>7895483732.50425</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>8702.257</t>
+          <t>8702257461.97285</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>8681.695</t>
+          <t>8681695129.21632</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>8363.094</t>
+          <t>8363093521.65983</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>8070.183</t>
+          <t>8070182770.72785</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>8544.563</t>
+          <t>8544562558.98054</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>8302.296</t>
+          <t>8302296393.77659</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>4157.117</t>
+          <t>4157116788.06015</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3918.203</t>
+          <t>3918202999.9989</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4072.668</t>
+          <t>4072668000.0005</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4284.869</t>
+          <t>4284869000.0004</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4400.057</t>
+          <t>4400057000.00028</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4434.13</t>
+          <t>4434130000.0001</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4274.174</t>
+          <t>4274174000.00003</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4282.962</t>
+          <t>4282962000.00007</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4410.964</t>
+          <t>4410963999.99973</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>4113.455</t>
+          <t>4113455000.00015</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>4127.597</t>
+          <t>4127597000.00018</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>4326.914</t>
+          <t>4326913999.99986</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>4449.578</t>
+          <t>4449578000.00096</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>4575.947</t>
+          <t>4575946999.99934</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>4454.165</t>
+          <t>4454165000.00103</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>4488.58</t>
+          <t>4488579999.99975</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>4478.093</t>
+          <t>4478093000.00107</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>4568.796</t>
+          <t>4568795999.99923</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>4659.401</t>
+          <t>4659400999.99904</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>4621.534</t>
+          <t>4621534090.24247</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>4391.906</t>
+          <t>4391906228.3783</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>4055.965</t>
+          <t>4055965284.58314</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>3914.062</t>
+          <t>3914062462.73114</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3921.409</t>
+          <t>3921408518.47882</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>3806.028</t>
+          <t>3806027827.0395</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>3845.528</t>
+          <t>3845528269.2394</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>4109.37</t>
+          <t>4109370153.98039</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>33652.466</t>
+          <t>33652466485.8443</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>29218.244</t>
+          <t>29218243600.0016</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29701.059</t>
+          <t>29701059440.0019</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>29378.636</t>
+          <t>29378636039.9991</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28529.224</t>
+          <t>28529224360.0008</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>28109.956</t>
+          <t>28109955640.0057</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25779.222</t>
+          <t>25779222039.9914</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>24960.842</t>
+          <t>24960841880.0017</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>25137.543</t>
+          <t>25137543080.0039</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>25471.69</t>
+          <t>25471690399.9989</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>25957.904</t>
+          <t>25957904439.9961</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>27523.023</t>
+          <t>27523023319.9992</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>28606.862</t>
+          <t>28606862439.996</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>29440.57</t>
+          <t>29440569599.9998</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>30626.083</t>
+          <t>30626083280</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>29659.855</t>
+          <t>29659855159.9964</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>29497.125</t>
+          <t>29497125320.0028</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>29484.885</t>
+          <t>29484884520.002</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>30095.401</t>
+          <t>30095400920.0011</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>25960.275</t>
+          <t>25960275242.1191</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>25159.391</t>
+          <t>25159391037.1464</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>28042.941</t>
+          <t>28042941303.7798</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>26265.477</t>
+          <t>26265477091.8502</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>28812.599</t>
+          <t>28812598727.8432</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>29498.321</t>
+          <t>29498320775.3631</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>29663.308</t>
+          <t>29663307556.8325</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>29877.761</t>
+          <t>29877760858.5723</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1551016.073</t>
+          <t>1551016072716.28</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>577496</t>
+          <t>577495999999.906</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>588306</t>
+          <t>588306000000.033</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>604175</t>
+          <t>604174999999.944</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>698030</t>
+          <t>698029999999.758</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>700208</t>
+          <t>700208000000.028</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>716599</t>
+          <t>716599000000.135</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>762391</t>
+          <t>762390999999.802</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>809364</t>
+          <t>809363999999.962</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>871179</t>
+          <t>871179000000.029</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>918656</t>
+          <t>918656000000.017</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>945169</t>
+          <t>945168999999.879</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>948168</t>
+          <t>948168000000.085</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1045459</t>
+          <t>1045459000000.1</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1044864</t>
+          <t>1044864000000.1</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1079549</t>
+          <t>1079549000000.08</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1115461</t>
+          <t>1115461000000.06</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1076200</t>
+          <t>1076200000000.13</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1054950</t>
+          <t>1054949999999.89</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1037512.807</t>
+          <t>1037512807230.07</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>1024370.485</t>
+          <t>1024370485374.47</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>1123437.035</t>
+          <t>1123437034858.71</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1111130.743</t>
+          <t>1111130742771.35</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>1146094.996</t>
+          <t>1146094995744.36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>1136763.101</t>
+          <t>1136763100735.28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>1222315.802</t>
+          <t>1222315802204.1</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1269912.792</t>
+          <t>1269912791772.38</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>283117.929</t>
+          <t>283117928660.332</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>195899</t>
+          <t>195898999999.973</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>206119</t>
+          <t>206119000000.008</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>208322</t>
+          <t>208322000000.006</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>209441</t>
+          <t>209441000000.063</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>210949</t>
+          <t>210949000000.003</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>214229</t>
+          <t>214229000000.011</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>214001</t>
+          <t>214000999999.968</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>225244</t>
+          <t>225243999999.979</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>228629</t>
+          <t>228628999999.995</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>225987</t>
+          <t>225986999999.999</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>230587</t>
+          <t>230587000000.011</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>233624</t>
+          <t>233623999999.988</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>250088</t>
+          <t>250087999999.998</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>258824</t>
+          <t>258824000000.031</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>273988</t>
+          <t>273988000000.003</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>289255</t>
+          <t>289255000000.004</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>293570</t>
+          <t>293570000000.022</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>292152</t>
+          <t>292151999999.982</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>284495.323</t>
+          <t>284495322784.564</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>276298.231</t>
+          <t>276298230970.686</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>319610.124</t>
+          <t>319610123782.832</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>290597.356</t>
+          <t>290597356244.036</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>302722.838</t>
+          <t>302722838437.698</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>270259.089</t>
+          <t>270259088722.965</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>264511.962</t>
+          <t>264511962122.899</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>259121.477</t>
+          <t>259121477325.377</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>427006.306</t>
+          <t>427006305889.841</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>305893</t>
+          <t>305892999999.924</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>303726</t>
+          <t>303725999999.956</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>304849</t>
+          <t>304848999999.953</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>306658</t>
+          <t>306657999999.961</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>312324</t>
+          <t>312324000000.077</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>302461</t>
+          <t>302460999999.982</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>304765</t>
+          <t>304764999999.889</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>308923</t>
+          <t>308922999999.931</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>301733</t>
+          <t>301733000000.058</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>308793</t>
+          <t>308792999999.987</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>313414</t>
+          <t>313414000000.036</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>317715</t>
+          <t>317715000000.013</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>320003</t>
+          <t>320002999999.994</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>325966</t>
+          <t>325966000000.015</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>325974</t>
+          <t>325973999999.976</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>324073</t>
+          <t>324073000000.062</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>330235</t>
+          <t>330234999999.905</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>330203</t>
+          <t>330203000000.062</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>339406.914</t>
+          <t>339406914217.666</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>290310.518</t>
+          <t>290310518367.437</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>270089.018</t>
+          <t>270089017662.905</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>268713.868</t>
+          <t>268713868433.452</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>297917.148</t>
+          <t>297917147937.803</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>321085.569</t>
+          <t>321085569008.149</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>358533.548</t>
+          <t>358533547517.478</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>369521.988</t>
+          <t>369521988326.851</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1152128.951</t>
+          <t>1152128950714.66</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>513668</t>
+          <t>513668000000.017</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>527164</t>
+          <t>527164000000.009</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>541782</t>
+          <t>541781999999.963</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>557220</t>
+          <t>557220000000.152</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>572673</t>
+          <t>572673000000.043</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>588924</t>
+          <t>588924000000.031</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>608937</t>
+          <t>608937000000.016</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>626418</t>
+          <t>626418000000.178</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>643870</t>
+          <t>643870000000.093</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>661153</t>
+          <t>661152999999.916</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>677546</t>
+          <t>677546000000.086</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>694189</t>
+          <t>694188999999.837</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>728739</t>
+          <t>728739000000.141</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>742967</t>
+          <t>742967000000.015</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>759096</t>
+          <t>759095999999.998</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>789675</t>
+          <t>789674999999.953</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>812305</t>
+          <t>812305000000.127</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>833344</t>
+          <t>833343999999.946</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>872184.635</t>
+          <t>872184635269.527</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>887118.65</t>
+          <t>887118649822.419</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>959002.733</t>
+          <t>959002732620.176</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>918913.862</t>
+          <t>918913861680.6</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>927625.88</t>
+          <t>927625879799.839</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>932634.105</t>
+          <t>932634105109.966</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>1023921.84</t>
+          <t>1023921840443.1</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1049544.496</t>
+          <t>1049544495879.78</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>116851.919</t>
+          <t>116851919394.413</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>52254</t>
+          <t>52254000000.011</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>52922000000.0035</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>54506</t>
+          <t>54506000000.0109</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>55142</t>
+          <t>55141999999.9973</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>55951</t>
+          <t>55951000000.0028</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>51432</t>
+          <t>51431999999.9928</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>57255</t>
+          <t>57254999999.9932</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>61680</t>
+          <t>61680000000.0178</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>67064</t>
+          <t>67063999999.9967</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>72206</t>
+          <t>72206000000.0016</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>74872</t>
+          <t>74872000000.0015</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>87939</t>
+          <t>87938999999.9931</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>93569</t>
+          <t>93569000000.0166</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>92014</t>
+          <t>92014000000.0256</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>99306</t>
+          <t>99306000000.0111</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>101400</t>
+          <t>101399999999.96</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>102375</t>
+          <t>102375000000.007</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>104591</t>
+          <t>104591000000.02</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>98166.866</t>
+          <t>98166866239.6902</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>93174.021</t>
+          <t>93174021172.3097</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>101909.567</t>
+          <t>101909566630.01</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>100128.783</t>
+          <t>100128782875.285</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>99892.368</t>
+          <t>99892367514.3548</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>100251.706</t>
+          <t>100251706101.657</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>108258.277</t>
+          <t>108258277152.907</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>112688.485</t>
+          <t>112688485131.496</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>abstract_labour.emp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
